--- a/artfynd/A 8107-2024 artfynd.xlsx
+++ b/artfynd/A 8107-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129755394</v>
       </c>
       <c r="B2" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129757918</v>
       </c>
       <c r="B3" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>129757904</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>129755794</v>
       </c>
       <c r="B5" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>129757908</v>
       </c>
       <c r="B6" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8107-2024 artfynd.xlsx
+++ b/artfynd/A 8107-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -804,7 +804,7 @@
         <v>129757918</v>
       </c>
       <c r="B3" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>129757904</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>129755794</v>
       </c>
       <c r="B5" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 8107-2024 artfynd.xlsx
+++ b/artfynd/A 8107-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 8107-2024 artfynd.xlsx
+++ b/artfynd/A 8107-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 8107-2024 artfynd.xlsx
+++ b/artfynd/A 8107-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129755394</v>
       </c>
       <c r="B2" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129757918</v>
       </c>
       <c r="B3" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>129757904</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>129755794</v>
       </c>
       <c r="B5" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>129757908</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8107-2024 artfynd.xlsx
+++ b/artfynd/A 8107-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129755394</v>
       </c>
       <c r="B2" t="n">
-        <v>56927</v>
+        <v>56930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129757918</v>
       </c>
       <c r="B3" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>129757904</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>129755794</v>
       </c>
       <c r="B5" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>129757908</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8107-2024 artfynd.xlsx
+++ b/artfynd/A 8107-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129757918</v>
       </c>
       <c r="B3" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>129757904</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>129755794</v>
       </c>
       <c r="B5" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 8107-2024 artfynd.xlsx
+++ b/artfynd/A 8107-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129757918</v>
       </c>
       <c r="B3" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>129757904</v>
       </c>
       <c r="B4" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>129755794</v>
       </c>
       <c r="B5" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 8107-2024 artfynd.xlsx
+++ b/artfynd/A 8107-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,67 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129755394</v>
+        <v>129757904</v>
       </c>
       <c r="B2" t="n">
-        <v>56931</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mellanberg, Mellanberg, Dlr</t>
+          <t>Mellanberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493256</v>
+        <v>493143</v>
       </c>
       <c r="R2" t="n">
-        <v>6805774</v>
+        <v>6806108</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,27 +746,18 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,39 +769,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129757918</v>
+        <v>129757939</v>
       </c>
       <c r="B3" t="n">
-        <v>78853</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493149</v>
+        <v>493126</v>
       </c>
       <c r="R3" t="n">
-        <v>6806115</v>
+        <v>6806127</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -902,14 +877,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129757904</v>
+        <v>129757954</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -940,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493143</v>
+        <v>493119</v>
       </c>
       <c r="R4" t="n">
-        <v>6806108</v>
+        <v>6806129</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,7 +981,7 @@
         <v>129755794</v>
       </c>
       <c r="B5" t="n">
-        <v>80200</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1088,7 @@
         <v>129757908</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,57 +1190,67 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129757911</v>
+        <v>129755394</v>
       </c>
       <c r="B7" t="n">
-        <v>5176</v>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102204</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mellanberg, Dlr</t>
+          <t>Mellanberg, Mellanberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493143</v>
+        <v>493256</v>
       </c>
       <c r="R7" t="n">
-        <v>6806108</v>
+        <v>6805774</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,18 +1277,27 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1315,10 +1309,325 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129757911</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5178</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mellanberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>493143</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6806108</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
           <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129757932</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mellanberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>493126</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6806127</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129757918</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mellanberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>493149</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6806115</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8107-2024 artfynd.xlsx
+++ b/artfynd/A 8107-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129757904</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129757939</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129757954</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129755794</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129757908</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,6 +1343,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129755394</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1420,6 +1455,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129757911</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1527,6 +1567,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129757932</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1628,8 +1673,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129757918</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>